--- a/docs/export-templates/AI问书_XX出版社_C端用户数据导出.xlsx
+++ b/docs/export-templates/AI问书_XX出版社_C端用户数据导出.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="127">
   <si>
     <t>机构 C 端用户</t>
   </si>
@@ -31,6 +31,9 @@
     <t>微信号</t>
   </si>
   <si>
+    <t>归属机构</t>
+  </si>
+  <si>
     <t>地区</t>
   </si>
   <si>
@@ -49,6 +52,9 @@
     <t>最新登录</t>
   </si>
   <si>
+    <t>注册时间</t>
+  </si>
+  <si>
     <t>微信昵称A</t>
   </si>
   <si>
@@ -58,13 +64,16 @@
     <t>wx_abc</t>
   </si>
   <si>
+    <t>XX 出版社</t>
+  </si>
+  <si>
     <t>上海 · 浦东</t>
   </si>
   <si>
     <t>女</t>
   </si>
   <si>
-    <t>会员</t>
+    <t>有效会员</t>
   </si>
   <si>
     <t>¥129.6</t>
@@ -73,6 +82,9 @@
     <t>2026-06-06 21:30:11</t>
   </si>
   <si>
+    <t>2026-01-12 10:03:22</t>
+  </si>
+  <si>
     <t>微信昵称B</t>
   </si>
   <si>
@@ -88,7 +100,7 @@
     <t>男</t>
   </si>
   <si>
-    <t>非会员</t>
+    <t>未开通会员</t>
   </si>
   <si>
     <t>¥0</t>
@@ -97,6 +109,9 @@
     <t>2026-06-01 10:02:45</t>
   </si>
   <si>
+    <t>2026-03-05 14:22:10</t>
+  </si>
+  <si>
     <t>用户0000</t>
   </si>
   <si>
@@ -109,6 +124,9 @@
     <t>2026-06-05 08:14:20</t>
   </si>
   <si>
+    <t>2025-12-20 09:41:35</t>
+  </si>
+  <si>
     <t>微信昵称C</t>
   </si>
   <si>
@@ -121,21 +139,33 @@
     <t>广州 · 天河</t>
   </si>
   <si>
+    <t>宽限期（待续费）</t>
+  </si>
+  <si>
     <t>¥59.7</t>
   </si>
   <si>
     <t>2026-06-06 18:22:03</t>
   </si>
   <si>
+    <t>2026-02-14 20:15:08</t>
+  </si>
+  <si>
     <t>用户5678</t>
   </si>
   <si>
     <t>137****5678</t>
   </si>
   <si>
+    <t>会员已过期</t>
+  </si>
+  <si>
     <t>2026-06-04 12:41:55</t>
   </si>
   <si>
+    <t>2026-04-01 08:30:54</t>
+  </si>
+  <si>
     <t>微信昵称D</t>
   </si>
   <si>
@@ -154,6 +184,9 @@
     <t>2026-06-06 09:05:18</t>
   </si>
   <si>
+    <t>2025-11-08 16:47:29</t>
+  </si>
+  <si>
     <t>微信昵称E</t>
   </si>
   <si>
@@ -166,6 +199,9 @@
     <t>2026-05-30 22:13:40</t>
   </si>
   <si>
+    <t>2026-05-02 12:09:17</t>
+  </si>
+  <si>
     <t>用户1357</t>
   </si>
   <si>
@@ -178,6 +214,9 @@
     <t>2026-06-05 16:48:27</t>
   </si>
   <si>
+    <t>2026-01-28 19:33:46</t>
+  </si>
+  <si>
     <t>微信昵称F</t>
   </si>
   <si>
@@ -196,6 +235,9 @@
     <t>2026-06-06 07:30:09</t>
   </si>
   <si>
+    <t>2025-12-02 07:56:03</t>
+  </si>
+  <si>
     <t>微信昵称G</t>
   </si>
   <si>
@@ -208,6 +250,9 @@
     <t>2026-05-28 11:19:51</t>
   </si>
   <si>
+    <t>2026-03-19 22:24:38</t>
+  </si>
+  <si>
     <t>用户2024</t>
   </si>
   <si>
@@ -220,6 +265,9 @@
     <t>2026-06-04 20:02:33</t>
   </si>
   <si>
+    <t>2026-02-06 11:18:52</t>
+  </si>
+  <si>
     <t>微信昵称H</t>
   </si>
   <si>
@@ -235,6 +283,9 @@
     <t>2026-06-02 14:55:12</t>
   </si>
   <si>
+    <t>2026-04-27 15:40:26</t>
+  </si>
+  <si>
     <t>微信昵称I</t>
   </si>
   <si>
@@ -253,6 +304,9 @@
     <t>2026-06-06 23:11:47</t>
   </si>
   <si>
+    <t>2025-10-16 13:27:44</t>
+  </si>
+  <si>
     <t>用户8080</t>
   </si>
   <si>
@@ -263,6 +317,81 @@
   </si>
   <si>
     <t>2026-06-03 08:44:21</t>
+  </si>
+  <si>
+    <t>2026-05-21 18:02:59</t>
+  </si>
+  <si>
+    <t>微信昵称J</t>
+  </si>
+  <si>
+    <t>186****3321</t>
+  </si>
+  <si>
+    <t>wx_j88</t>
+  </si>
+  <si>
+    <t>XX 少儿分社</t>
+  </si>
+  <si>
+    <t>上海 · 徐汇</t>
+  </si>
+  <si>
+    <t>¥99.4</t>
+  </si>
+  <si>
+    <t>2026-08-05 20:12:40</t>
+  </si>
+  <si>
+    <t>2026-03-11 09:20:31</t>
+  </si>
+  <si>
+    <t>用户6611</t>
+  </si>
+  <si>
+    <t>185****6611</t>
+  </si>
+  <si>
+    <t>¥29.9</t>
+  </si>
+  <si>
+    <t>2026-08-04 15:41:02</t>
+  </si>
+  <si>
+    <t>2026-04-18 11:05:44</t>
+  </si>
+  <si>
+    <t>微信昵称K</t>
+  </si>
+  <si>
+    <t>158****9902</t>
+  </si>
+  <si>
+    <t>wx_k99</t>
+  </si>
+  <si>
+    <t>XX 教辅分社</t>
+  </si>
+  <si>
+    <t>苏州 · 园区</t>
+  </si>
+  <si>
+    <t>2026-08-02 10:33:15</t>
+  </si>
+  <si>
+    <t>2026-06-01 17:28:09</t>
+  </si>
+  <si>
+    <t>用户7745</t>
+  </si>
+  <si>
+    <t>150****7745</t>
+  </si>
+  <si>
+    <t>2026-07-30 21:09:58</t>
+  </si>
+  <si>
+    <t>2026-02-25 08:52:17</t>
   </si>
 </sst>
 </file>
@@ -735,20 +864,21 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="3" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="11" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -760,8 +890,10 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-    </row>
-    <row r="2" ht="25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -773,8 +905,10 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-    </row>
-    <row r="3" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -786,8 +920,10 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -815,419 +951,649 @@
       <c r="I4" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="6">
+        <v>3</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="6">
-        <v>3</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="5" t="s">
+      <c r="E6" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="9">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="6">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="G8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="9">
+        <v>2</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="9">
+      <c r="H10" s="9">
+        <v>5</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="6">
         <v>0</v>
       </c>
-      <c r="H6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="I11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" s="9">
+        <v>1</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="G13" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="6">
+        <v>4</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="9">
+        <v>0</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="6">
+        <v>2</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="H16" s="9">
+        <v>0</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="6">
+      <c r="E17" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="6">
+        <v>6</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="9">
         <v>1</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="I18" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="6">
+        <v>2</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" s="9">
+        <v>0</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" s="6">
+        <v>0</v>
+      </c>
+      <c r="I21" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="9">
-        <v>2</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="6">
-        <v>0</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="9">
-        <v>5</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="J21" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11" s="6">
-        <v>0</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" s="9">
+      <c r="H22" s="9">
         <v>1</v>
       </c>
-      <c r="H12" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13" s="6">
-        <v>4</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G14" s="9">
-        <v>0</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="I22" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15" s="6">
-        <v>2</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G16" s="9">
-        <v>0</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" s="6">
-        <v>6</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" s="9">
-        <v>1</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>83</v>
+      <c r="J22" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I4"/>
+  <autoFilter ref="A4:K4"/>
   <mergeCells count="3">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
